--- a/DATA/MASTER/C11_MASTER/Universo_Analitico/universo_analitico_ipml.xlsx
+++ b/DATA/MASTER/C11_MASTER/Universo_Analitico/universo_analitico_ipml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,16 @@
           <t>Puntaje_Calidad</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,11 +544,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.898</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -547,12 +557,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -577,6 +587,12 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,20 +609,20 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31.915</v>
+        <v>36.388</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -615,12 +631,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -645,6 +661,12 @@
       <c r="P3" t="n">
         <v>1</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -670,11 +692,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10.573</v>
+        <v>13.221</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -683,12 +705,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -713,6 +735,12 @@
       <c r="P4" t="n">
         <v>1</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,20 +757,20 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>36.048</v>
+        <v>82.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -751,12 +779,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -781,6 +809,12 @@
       <c r="P5" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -806,11 +840,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7.128</v>
+        <v>9.391</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -819,12 +853,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -849,6 +883,12 @@
       <c r="P6" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -874,11 +914,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.477</v>
+        <v>2.574</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -887,12 +927,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -917,6 +957,12 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -942,11 +988,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.704</v>
+        <v>2.449</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -955,12 +1001,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -985,6 +1031,12 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1010,25 +1062,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5.779</v>
+        <v>4.188</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1053,6 +1105,12 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1078,11 +1136,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.152</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1091,12 +1149,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,6 +1179,12 @@
       <c r="P10" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1146,11 +1210,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.265</v>
+        <v>2.084</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1159,12 +1223,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1189,6 +1253,12 @@
       <c r="P11" t="n">
         <v>1</v>
       </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1202,10 +1272,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1214,25 +1284,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11.557</v>
+        <v>2.114</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1252,9 +1322,15 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>100</v>
+        <v>63.64</v>
       </c>
       <c r="P12" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1270,10 +1346,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1282,25 +1358,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13.982</v>
+        <v>2.144</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1325,6 +1401,12 @@
       <c r="P13" t="n">
         <v>1</v>
       </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1338,25 +1420,39 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1182.398</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Demográfica</t>
@@ -1379,6 +1475,12 @@
       <c r="P14" t="n">
         <v>1</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1392,39 +1494,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1329.161</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1449,6 +1549,12 @@
       <c r="P15" t="n">
         <v>1</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1462,10 +1568,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1474,25 +1580,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4.434</v>
+        <v>8.381</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1517,6 +1623,12 @@
       <c r="P16" t="n">
         <v>0.091</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1530,39 +1642,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>37.091</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1587,6 +1697,12 @@
       <c r="P17" t="n">
         <v>1</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1600,39 +1716,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3.619</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1657,6 +1771,12 @@
       <c r="P18" t="n">
         <v>1</v>
       </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1670,39 +1790,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>42.952</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1727,6 +1845,12 @@
       <c r="P19" t="n">
         <v>1</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1740,39 +1864,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>32.439</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1797,6 +1919,12 @@
       <c r="P20" t="n">
         <v>1</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1810,39 +1938,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3.032</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1867,6 +1993,12 @@
       <c r="P21" t="n">
         <v>1</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1880,39 +2012,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>7.181</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1937,6 +2067,12 @@
       <c r="P22" t="n">
         <v>1</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1962,25 +2098,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>2354914.55</v>
-      </c>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>No Calculado</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>VIF no calculable por varianza nula de la variable.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Evaluar por separado debido a varianza nula; el VIF no es calculable.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2005,6 +2139,12 @@
       <c r="P23" t="n">
         <v>0.182</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2018,37 +2158,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Baja redundancia estructural.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.372</v>
+        <v>6.742</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2073,6 +2213,12 @@
       <c r="P24" t="n">
         <v>0.182</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2086,37 +2232,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>5.555</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2141,6 +2287,12 @@
       <c r="P25" t="n">
         <v>0.182</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2166,11 +2318,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.027</v>
+        <v>1.028</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2179,12 +2331,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2209,6 +2361,12 @@
       <c r="P26" t="n">
         <v>0.165</v>
       </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2222,23 +2380,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baja redundancia estructural.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>22.078</v>
+        <v>22.148</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2247,12 +2405,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2277,6 +2435,12 @@
       <c r="P27" t="n">
         <v>0.095</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2290,37 +2454,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1.934</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2345,6 +2509,12 @@
       <c r="P28" t="n">
         <v>0.049</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2370,11 +2540,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.97</v>
+        <v>2.999</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2383,12 +2553,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2413,6 +2583,12 @@
       <c r="P29" t="n">
         <v>0.093</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2429,20 +2605,20 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>14.153</v>
+        <v>14.559</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2451,12 +2627,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2481,6 +2657,12 @@
       <c r="P30" t="n">
         <v>0.093</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2494,10 +2676,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2506,11 +2688,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10.296</v>
+        <v>10.278</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2519,12 +2701,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2549,6 +2731,12 @@
       <c r="P31" t="n">
         <v>0.055</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2562,10 +2750,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2574,11 +2762,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7.427</v>
+        <v>7.54</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2587,12 +2775,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2617,6 +2805,12 @@
       <c r="P32" t="n">
         <v>0.095</v>
       </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2630,10 +2824,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2642,11 +2836,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.705</v>
+        <v>2.722</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2655,12 +2849,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2685,6 +2879,12 @@
       <c r="P33" t="n">
         <v>0.095</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2698,10 +2898,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2710,11 +2910,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.883</v>
+        <v>2.965</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2723,12 +2923,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2753,6 +2953,12 @@
       <c r="P34" t="n">
         <v>0.095</v>
       </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2766,10 +2972,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2778,11 +2984,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.619</v>
+        <v>1.645</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2791,12 +2997,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2821,6 +3027,12 @@
       <c r="P35" t="n">
         <v>0.064</v>
       </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2846,11 +3058,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.815</v>
+        <v>2.878</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2859,12 +3071,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2888,6 +3100,12 @@
       </c>
       <c r="P36" t="n">
         <v>0.095</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
